--- a/output/pdf_financials_xlsx/IVS.xlsx
+++ b/output/pdf_financials_xlsx/IVS.xlsx
@@ -7369,22 +7369,22 @@
         <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>0.017663</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>0.058151</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>0.057424</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>0.024177</v>
       </c>
       <c r="P118" s="3" t="n">
         <v>0</v>
@@ -27465,7 +27465,11 @@
           <t>Stock-based compensation included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -29651,7 +29655,11 @@
           <t>Non-cash exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IVS.xlsx
+++ b/output/pdf_financials_xlsx/IVS.xlsx
@@ -1047,25 +1047,25 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.034925</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001144</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.020793</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.011163</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.012643</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.070066</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2007,25 +2007,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.538727</v>
+        <v>-0.503802</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.754231</v>
+        <v>-1.753087</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.10155</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.924699</v>
+        <v>-0.945492</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>4.074046</v>
+        <v>4.062883</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.552096</v>
+        <v>-2.564739</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.92121</v>
+        <v>-0.991276</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-3.629636</v>
@@ -2123,25 +2123,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.538727</v>
+        <v>-0.503802</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.754231</v>
+        <v>-1.753087</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.10155</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.924699</v>
+        <v>-0.945492</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.074046</v>
+        <v>4.062883</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.552096</v>
+        <v>-2.564739</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.92121</v>
+        <v>-0.991276</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-3.629636</v>
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-324.5540744303938</v>
+        <v>-324.3424205141488</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>32.49811702390355</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-17.74116897680714</v>
+        <v>-18.14010109042979</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
         <v>0.445697</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.357778</v>
+        <v>0.032789</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.177203</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>2.863966</v>
@@ -2439,22 +2439,22 @@
         <v>2.412134</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.905429</v>
+        <v>0.058935</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.7319639999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.687361</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.548194</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.026016</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.43737</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0.724917</v>
@@ -2537,10 +2537,10 @@
         <v>0.445697</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.357778</v>
+        <v>0.032789</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.177203</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.863966</v>
@@ -2555,22 +2555,22 @@
         <v>2.412134</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.905429</v>
+        <v>0.058935</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.7319639999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.687361</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.548194</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.026016</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.2548</v>
+        <v>0.69217</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0.724917</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.352133</v>
+        <v>0.17493</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.03368</v>
@@ -3251,22 +3251,22 @@
         <v>0.402717</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0</v>
+        <v>0.019451</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.769147</v>
+        <v>0.037183</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.7100070000000001</v>
+        <v>0.022646</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.561555</v>
+        <v>0.013361</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.040087</v>
+        <v>0.014071</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.456641</v>
+        <v>0.019271</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.019012</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -50004,7 +50004,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -50921,7 +50921,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -52133,7 +52133,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -52337,7 +52337,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -55129,7 +55129,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -56646,7 +56646,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -61783,7 +61783,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E534" s="5" t="n">
@@ -61886,7 +61886,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E535" s="5" t="n">

--- a/output/pdf_financials_xlsx/IVS.xlsx
+++ b/output/pdf_financials_xlsx/IVS.xlsx
@@ -4396,19 +4396,19 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.088412</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.015507</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.01768</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.02317</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
@@ -6484,16 +6484,16 @@
         <v>-0.151333</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.05225</v>
+        <v>0.008148000000000001</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.002402</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.010356</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001072</v>
       </c>
       <c r="I103" s="3" t="n">
         <v>0.007347</v>
@@ -6902,7 +6902,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.003629</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -6920,10 +6920,10 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>-0.003844</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.003844</v>
       </c>
       <c r="Q110" s="3" t="n">
         <v>0</v>
@@ -6954,13 +6954,13 @@
         <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.038346</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.031037</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00171</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -8332,13 +8332,13 @@
         <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.038346</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.031037</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00171</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -8399,10 +8399,10 @@
         </is>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-1.998368</v>
+        <v>-2.029405</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.112384</v>
+        <v>-1.114094</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.790559</v>
@@ -24980,7 +24980,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -27267,7 +27271,11 @@
           <t>CEBA loan accretion expense (note 7)</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -27665,7 +27673,11 @@
           <t>CEBA loan accretion expense (note 8)</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -31271,7 +31283,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -31473,7 +31489,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -32174,7 +32194,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -34453,7 +34477,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -35243,7 +35271,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -35536,7 +35568,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -37306,7 +37342,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -39851,7 +39891,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -41990,7 +42034,11 @@
           <t>Future income taxes (recovery)</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E337" s="5" t="n">
         <v>-0.34104</v>
       </c>
